--- a/artfynd/A 61747-2021 artfynd.xlsx
+++ b/artfynd/A 61747-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61747-2021 artfynd.xlsx
+++ b/artfynd/A 61747-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113886422</v>
+        <v>113887755</v>
       </c>
       <c r="B5" t="n">
-        <v>89406</v>
+        <v>91605</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,25 +1027,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>644655</v>
+        <v>644664</v>
       </c>
       <c r="R5" t="n">
-        <v>7202690</v>
+        <v>7202688</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,117 +1123,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>113887755</v>
-      </c>
-      <c r="B6" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Rusele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>644664</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7202688</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2023-10-26</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2023-10-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61747-2021 artfynd.xlsx
+++ b/artfynd/A 61747-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96482586</v>
+        <v>96482582</v>
       </c>
       <c r="B2" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mittisundsmarken, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>644632.3754999642</v>
+        <v>644656</v>
       </c>
       <c r="R2" t="n">
-        <v>7202491.525075493</v>
+        <v>7202690</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,28 +743,17 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96482582</v>
+        <v>113886422</v>
       </c>
       <c r="B3" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,17 +800,21 @@
           <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mittisundsmarken, Ly lm</t>
+          <t>Rusele, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>644655.9690155121</v>
+        <v>644655</v>
       </c>
       <c r="R3" t="n">
-        <v>7202689.88395254</v>
+        <v>7202690</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,22 +841,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,12 +866,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Larsson, Ingalill  Larsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -906,16 +881,11 @@
         <v>96482591</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -943,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>644665.8361328593</v>
+        <v>644666</v>
       </c>
       <c r="R4" t="n">
-        <v>7202688.236426919</v>
+        <v>7202688</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,19 +946,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,16 +978,11 @@
         <v>113887755</v>
       </c>
       <c r="B5" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1123,6 +1078,107 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96482586</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mittisundsmarken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>644632</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7202492</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Ingalill  Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61747-2021 artfynd.xlsx
+++ b/artfynd/A 61747-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482582</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113886422</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482591</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887755</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,8 +1204,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482586</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>